--- a/samples/datos_dummy.xlsx
+++ b/samples/datos_dummy.xlsx
@@ -76,7 +76,7 @@
     <t>Formación</t>
   </si>
   <si>
-    <t>Certificación Azure</t>
+    <t>Certificación en la nube</t>
   </si>
   <si>
     <t>Cyberdyne S.A.</t>
@@ -178,7 +178,7 @@
     <t>Raúl Gómez</t>
   </si>
   <si>
-    <t>Taller Excel avanzado</t>
+    <t>Taller de hojas de cálculo</t>
   </si>
   <si>
     <t>Globex S.A.</t>
@@ -187,7 +187,7 @@
     <t>Wonka S.L.</t>
   </si>
   <si>
-    <t>Curso Power BI</t>
+    <t>Curso de análisis de datos</t>
   </si>
   <si>
     <t>Jorge Sánchez</t>
